--- a/13776_Cuenca_Chancay-Lambayeque/_raw_reportes_xlsx/IDConfig_67577_completo.xlsx
+++ b/13776_Cuenca_Chancay-Lambayeque/_raw_reportes_xlsx/IDConfig_67577_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb19ab36edf6947cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re0c3aa97f13b429d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3196</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2849</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2849</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3196</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3565</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3955</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5256</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3565</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3565</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/13776_Cuenca_Chancay-Lambayeque/_raw_reportes_xlsx/IDConfig_67577_completo.xlsx
+++ b/13776_Cuenca_Chancay-Lambayeque/_raw_reportes_xlsx/IDConfig_67577_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re0c3aa97f13b429d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Ra414d836a5a840d7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4781</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7865</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6233</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1036</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0356</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6233</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4801</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5256</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7299</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3985</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7865</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8289</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.4060</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5734</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5256</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6755</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9065</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3955</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3565</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4801</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4801</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4801</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4801</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4801</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5734</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5256</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2522</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2522</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2522</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2849</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2849</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3955</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5256</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2849</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2522</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2849</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2849</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2849</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3196</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3196</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3196</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -20155,6 +20875,6021 @@
       </x:c>
       <x:c s="3">
         <x:v>     21.4618</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6789</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1007</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6169</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.9666</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6169</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7274</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3865</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6165</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9493</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3824</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4032</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8197</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4781</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2464</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1738</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1036</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1036</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1738</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3213</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2464</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3213</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4781</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3985</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3985</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5599</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3985</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3985</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5599</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7274</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5599</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7307</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7816</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.9342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4781</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4781</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5599</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7307</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8197</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3163</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1936</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9556</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1007</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4032</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6169</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8403</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3163</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0087</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5654</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1041</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4539</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0087</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.0639</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.9329</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.8420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.4791</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6169</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0734</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1936</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1364</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8257</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8403</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8403</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.8316</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5315</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1936</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8403</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0734</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3865</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.3363</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.9743</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6789</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.4282</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7816</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3865</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.2884</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.6792</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1364</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.7663</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.5156</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.2413</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.9779</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1738</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2464</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1738</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1738</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0356</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1036</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0356</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1036</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1036</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2464</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1036</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1738</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3213</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3985</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5599</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5599</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7307</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6442</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5599</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6442</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6442</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6442</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8197</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5089</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5089</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6169</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1007</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1007</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4032</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4032</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.8316</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4414</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2939</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.4734</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3617</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1607</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7307</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7307</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6442</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8197</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8197</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5315</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8197</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1007</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1007</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5089</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1936</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4032</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4414</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8403</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4032</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5089</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5089</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6169</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7274</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7274</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8403</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9556</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0734</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0734</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1936</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4414</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.9666</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.2922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.9666</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.9666</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4539</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.7663</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6789</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7816</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4539</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.6227</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6165</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0087</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9804</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.5324</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.2629</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8289</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5315</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8289</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6165</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.6227</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.0597</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.6227</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1607</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4539</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7816</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8257</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9622</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.9342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.5156</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.0319</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     64.6873</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.4750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.4482</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     48.5484</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     81.2580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.4507</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1919</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9622</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.1345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.4791</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.9145</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7816</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9493</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0087</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.6911</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.6792</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.1798</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.0585</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.2413</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.8420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.2130</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.4482</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.5156</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.0585</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5654</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.2130</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.6911</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.1494</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.1345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.3564</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.2188</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.3027</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.9580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.6168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.1642</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.0319</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.4734</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.1372</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.4744</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.8001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/04/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.0777</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.0321</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     44.0361</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8671</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     52.2198</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.8281</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.7968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.5324</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     54.9292</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     73.3611</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.1345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.7083</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.4028</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.1859</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.9329</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3824</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7716</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.2130</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5654</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.4507</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7716</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.0639</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.4482</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.0597</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.6168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.1494</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6677</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.7083</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.8910</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     39.2954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/03/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     48.0355</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6677</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.1372</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     41.6300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.5759</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.6637</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9622</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8257</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1607</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.8420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.8645</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.7968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.4507</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.8182</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.2995</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8671</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     40.2206</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.4028</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.2922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5690</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5690</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.8316</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/02/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.9666</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8289</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6165</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3824</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.9357</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.4734</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6165</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3617</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.7663</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1936</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3163</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2939</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.7454</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.6227</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6789</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9556</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0734</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4414</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1041</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8289</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.8316</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3865</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2939</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2939</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.4060</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/01/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6165</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1194</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9804</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.6911</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4539</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7816</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.7663</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.4060</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.8808</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     43.0651</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     52.2198</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     46.0128</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.4618</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2939</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5315</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7816</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9622</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.1859</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.6168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9493</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5315</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3824</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.9342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.9342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5690</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/12/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9493</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/11/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.5156</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/11/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4414</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/11/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.9666</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/11/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1041</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/11/2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6789</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
